--- a/modelo/Modelo_Valoracion.xlsx
+++ b/modelo/Modelo_Valoracion.xlsx
@@ -21,12 +21,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.00&quot;x&quot;"/>
     <numFmt numFmtId="165" formatCode="$#,##0.00"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="+0%;-0%;0%"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -100,6 +101,11 @@
     <font>
       <name val="Arial"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="7">
@@ -175,7 +181,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -271,6 +277,21 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -661,7 +682,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B16"/>
+  <dimension ref="A2:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -696,50 +717,60 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="48" customHeight="1">
       <c r="B8" s="4" t="inlineStr">
         <is>
+          <t>Novedad: la Calculadora ahora fija sola los 3 múltiplos de salida (Negativo/Base/Optimista) con una regla derivada estadísticamente de los 55 casos (ver anexo al Paso 5 en METODOLOGIA.md). Puedes ajustarla con la columna "Ajuste manual" junto a cada múltiplo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="34" customHeight="1"/>
+    <row r="10">
+      <c r="B10" s="4" t="inlineStr">
+        <is>
           <t>• Checklist Cualitativo: Lista de verificación de 14 puntos + scorecard de moat + evaluación de riesgo, para completar junto con la Calculadora antes de decidir una posición.</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
-      <c r="B9" s="4" t="inlineStr">
+    <row r="11">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>• Casos de Estudio: Tabla con los 55 casos históricos ya analizados: múltiplos usados, precios objetivo, zonas de valor, conclusión y resultado. Úsala para consultar rápidamente cualquier caso pasado, o como inspiración de rangos de múltiplos por sector.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="B11" s="3" t="inlineStr">
+    <row r="12"/>
+    <row r="13">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Código de colores</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" s="5" t="inlineStr">
+    <row r="14">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>Amarillo = celda para llenar (input tuyo)</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" s="6" t="inlineStr">
+    <row r="15">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>Azul = valor de ejemplo / dato hardcodeado documentado</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="7" t="inlineStr">
+    <row r="16">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>Negro = fórmula (se recalcula sola, no la edites)</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="8" t="inlineStr">
+    <row r="17"/>
+    <row r="18">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>Nota: este modelo organiza información y automatiza cálculos con fines educativos y de seguimiento personal. No constituye asesoría financiera ni recomendación de inversión.</t>
         </is>
@@ -756,7 +787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:F32"/>
+  <dimension ref="B1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -765,6 +796,7 @@
     <col width="34" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -964,6 +996,11 @@
       <c r="F14" s="27" t="n">
         <v>6</v>
       </c>
+      <c r="G14" s="41" t="inlineStr">
+        <is>
+          <t>Ajuste manual</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="B15" s="12" t="inlineStr">
@@ -974,13 +1011,17 @@
       <c r="C15" s="26" t="n">
         <v>25</v>
       </c>
-      <c r="E15" s="12" t="inlineStr">
-        <is>
-          <t>Múltiplo escenario Negativo</t>
-        </is>
-      </c>
-      <c r="F15" s="26" t="n">
-        <v>13</v>
+      <c r="E15" s="42" t="inlineStr">
+        <is>
+          <t>Múltiplo Negativo (auto = mult. actual)</t>
+        </is>
+      </c>
+      <c r="F15" s="43">
+        <f>C14*(1+G15)</f>
+        <v/>
+      </c>
+      <c r="G15" s="44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -993,13 +1034,17 @@
         <f>C14/C15-1</f>
         <v/>
       </c>
-      <c r="E16" s="12" t="inlineStr">
-        <is>
-          <t>Múltiplo escenario Base</t>
-        </is>
-      </c>
-      <c r="F16" s="26" t="n">
-        <v>20</v>
+      <c r="E16" s="42" t="inlineStr">
+        <is>
+          <t>Múltiplo Base (auto = 0.78×prom. histórico)</t>
+        </is>
+      </c>
+      <c r="F16" s="43">
+        <f>0.78*C15*(1+G16)</f>
+        <v/>
+      </c>
+      <c r="G16" s="44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1011,13 +1056,17 @@
       <c r="C17" s="26" t="n">
         <v>12</v>
       </c>
-      <c r="E17" s="12" t="inlineStr">
-        <is>
-          <t>Múltiplo escenario Optimista</t>
-        </is>
-      </c>
-      <c r="F17" s="26" t="n">
-        <v>25</v>
+      <c r="E17" s="42" t="inlineStr">
+        <is>
+          <t>Múltiplo Optimista (auto = 0.92×prom. histórico)</t>
+        </is>
+      </c>
+      <c r="F17" s="43">
+        <f>0.92*C15*(1+G17)</f>
+        <v/>
+      </c>
+      <c r="G17" s="44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
@@ -1204,8 +1253,21 @@
     </row>
     <row r="31"/>
     <row r="32"/>
+    <row r="34">
+      <c r="B34" s="45" t="inlineStr">
+        <is>
+          <t>Regla automática de múltiplos de salida (Paso 5 de METODOLOGIA.md, anexo): calculada estadísticamente comparando, en 15-18 de los 55 casos de estudio con datos completos, el múltiplo implícito de cada escenario (precio objetivo ÷ EPS/FCF proyectado) contra el múltiplo actual y el promedio histórico de cada caso. Resultado: Negativo ≈ 1.00× el múltiplo actual (rango 0.70x-1.30x); Base ≈ 0.78× el promedio histórico (rango 0.56x-1.01x); Optimista ≈ 0.92× el promedio histórico (rango 0.65x-1.23x). Confianza MEDIA: es un ancla estadística de lo que este inversionista terminó haciendo en la práctica, no una fórmula que haya aplicado mecánicamente él mismo (él ajusta por calidad del negocio y convicción). Usa la columna 'Ajuste manual' para moverte, ej. -10% a -20% en hipótesis 'Especulativas' (así se comportaron AMD, NVO y otras especulativas del historial), o +X% si tienes convicción alta de que el negocio merece re-ratear por encima de su propia historia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="B34:G39"/>
     <mergeCell ref="B30:F32"/>
   </mergeCells>
   <conditionalFormatting sqref="F5">
